--- a/projects/ecm-compute/v1.0.0/export/资源池容量/资源池容量_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/资源池容量/资源池容量_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -582,6 +582,28 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>e_entity_0_resourceType</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>${entity_0_resourceType}</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>由 前置 API: products 提取 (path: entity[0].resourceType)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
